--- a/data/industry/CFM/RDIMM.xlsx
+++ b/data/industry/CFM/RDIMM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDDBB58-FEFE-4540-A035-11D1829F2F67}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1C30EE-F3FA-4AF0-B8CE-1F0469B40FF7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 RDIMM 16GB 3200" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="8">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -66,12 +66,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -126,50 +124,47 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -451,13 +446,13 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="5"/>
-    <col min="7" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="12"/>
+    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -473,321 +468,353 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>45846</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>45846</v>
       </c>
-      <c r="C2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="11">
         <v>160</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="11">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>45860</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>45860</v>
       </c>
-      <c r="C3" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11">
         <v>70</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="11">
         <v>160</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="11">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>45874</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>45874</v>
       </c>
-      <c r="C4" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11">
         <v>70</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <v>160</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>45909</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>45909</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="11">
         <v>85</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="11">
         <v>160</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="11">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>45944</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>45944</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="11">
         <v>120</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="11">
         <v>180</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="11">
         <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>45972</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>45972</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="11">
         <v>200</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="11">
         <v>250</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="11">
         <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>46000</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>46000</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11">
         <v>200</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="11">
         <v>300</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="11">
         <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>46028</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>46028</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="11">
         <v>240</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="11">
         <v>340</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="11">
         <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="A10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="11">
+        <v>240</v>
+      </c>
+      <c r="F10" s="11">
+        <v>350</v>
+      </c>
+      <c r="G10" s="11">
+        <v>300</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="A11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="11">
+        <v>240</v>
+      </c>
+      <c r="F11" s="11">
+        <v>350</v>
+      </c>
+      <c r="G11" s="11">
+        <v>300</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -800,13 +827,13 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="5"/>
-    <col min="7" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="12"/>
+    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -822,321 +849,353 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>45846</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>45846</v>
       </c>
-      <c r="C2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="11">
         <v>110</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="11">
         <v>170</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="11">
         <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>45860</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>45860</v>
       </c>
-      <c r="C3" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11">
         <v>110</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="11">
         <v>170</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="11">
         <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>45874</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>45874</v>
       </c>
-      <c r="C4" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11">
         <v>110</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <v>170</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>45909</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>45909</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="11">
         <v>135</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="11">
         <v>210</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="11">
         <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>45944</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>45944</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="11">
         <v>180</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="11">
         <v>240</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="11">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>45972</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>45972</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="11">
         <v>260</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="11">
         <v>400</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="11">
         <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>46000</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>46000</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11">
         <v>280</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="11">
         <v>420</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="11">
         <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>46028</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>46028</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="11">
         <v>280</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="11">
         <v>500</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="11">
         <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="A10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="11">
+        <v>280</v>
+      </c>
+      <c r="F10" s="11">
+        <v>730</v>
+      </c>
+      <c r="G10" s="11">
+        <v>450</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="A11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="11">
+        <v>280</v>
+      </c>
+      <c r="F11" s="11">
+        <v>730</v>
+      </c>
+      <c r="G11" s="11">
+        <v>450</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1149,13 +1208,14 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="5"/>
-    <col min="7" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="12"/>
+    <col min="6" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1171,321 +1231,353 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>45846</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>45846</v>
       </c>
-      <c r="C2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="11">
         <v>195</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="11">
         <v>260</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="11">
         <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>45860</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>45860</v>
       </c>
-      <c r="C3" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11">
         <v>195</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="11">
         <v>260</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="11">
         <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>45874</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>45874</v>
       </c>
-      <c r="C4" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11">
         <v>195</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <v>260</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>45909</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>45909</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="11">
         <v>230</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="11">
         <v>300</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="11">
         <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>45944</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>45944</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="11">
         <v>260</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="11">
         <v>360</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="11">
         <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>45972</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>45972</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="11">
         <v>440</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="11">
         <v>540</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="11">
         <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>46000</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>46000</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11">
         <v>480</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="11">
         <v>580</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="11">
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>46028</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>46028</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="11">
         <v>500</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="11">
         <v>800</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="11">
         <v>650</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="A10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="11">
+        <v>600</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="11">
+        <v>800</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="A11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="11">
+        <v>600</v>
+      </c>
+      <c r="F11" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="11">
+        <v>800</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1498,13 +1590,13 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="5"/>
-    <col min="7" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="12"/>
+    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1520,321 +1612,353 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>45846</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>45846</v>
       </c>
-      <c r="C2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="11">
         <v>135</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="11">
         <v>155</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="11">
         <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>45860</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>45860</v>
       </c>
-      <c r="C3" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11">
         <v>135</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="11">
         <v>155</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="11">
         <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>45874</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>45874</v>
       </c>
-      <c r="C4" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11">
         <v>135</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <v>155</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>45909</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>45909</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="11">
         <v>135</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="11">
         <v>155</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="11">
         <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>45944</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>45944</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="11">
         <v>160</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="11">
         <v>200</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="11">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>45972</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>45972</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="11">
         <v>220</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="11">
         <v>300</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="11">
         <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>46000</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>46000</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11">
         <v>240</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="11">
         <v>400</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="11">
         <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>46028</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>46028</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="11">
         <v>350</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="11">
         <v>450</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="11">
         <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="A10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="11">
+        <v>490</v>
+      </c>
+      <c r="F10" s="11">
+        <v>800</v>
+      </c>
+      <c r="G10" s="11">
+        <v>500</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="A11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="11">
+        <v>490</v>
+      </c>
+      <c r="F11" s="11">
+        <v>800</v>
+      </c>
+      <c r="G11" s="11">
+        <v>500</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1847,14 +1971,14 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="5"/>
-    <col min="6" max="6" width="10.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="12"/>
+    <col min="6" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1870,321 +1994,353 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>45846</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>45846</v>
       </c>
-      <c r="C2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="11">
         <v>250</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="11">
         <v>280</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="11">
         <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>45860</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>45860</v>
       </c>
-      <c r="C3" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11">
         <v>250</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="11">
         <v>280</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="11">
         <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>45874</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>45874</v>
       </c>
-      <c r="C4" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11">
         <v>250</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <v>280</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>45909</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>45909</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="11">
         <v>250</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="11">
         <v>280</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="11">
         <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>45944</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>45944</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="11">
         <v>280</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="11">
         <v>360</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="11">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>45972</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>45972</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="11">
         <v>440</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="11">
         <v>500</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="11">
         <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>46000</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>46000</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11">
         <v>450</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="11">
         <v>800</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="11">
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>46028</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>46028</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="11">
         <v>675</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="11">
         <v>1200</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="11">
         <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="A10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="11">
+        <v>830</v>
+      </c>
+      <c r="F10" s="11">
+        <v>2500</v>
+      </c>
+      <c r="G10" s="11">
+        <v>920</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="A11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="11">
+        <v>830</v>
+      </c>
+      <c r="F11" s="11">
+        <v>2500</v>
+      </c>
+      <c r="G11" s="11">
+        <v>920</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2197,13 +2353,13 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -2219,321 +2375,353 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>45846</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>45846</v>
       </c>
-      <c r="C2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="11">
         <v>390</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="11">
         <v>430</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="11">
         <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>45860</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>45860</v>
       </c>
-      <c r="C3" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11">
         <v>390</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="11">
         <v>430</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="11">
         <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>45874</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>45874</v>
       </c>
-      <c r="C4" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11">
         <v>395</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <v>435</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>45909</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>45909</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="11">
         <v>395</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="11">
         <v>435</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="11">
         <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>45944</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>45944</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="11">
         <v>460</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="11">
         <v>500</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="11">
         <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>45972</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>45972</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="11">
         <v>710</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="11">
         <v>850</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="11">
         <v>740</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>46000</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>46000</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11">
         <v>720</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="11">
         <v>1700</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="11">
         <v>800</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>46028</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>46028</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="11">
         <v>1080</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="11">
         <v>2000</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="11">
         <v>1300</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="A10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46063</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="11">
+        <v>1350</v>
+      </c>
+      <c r="F10" s="11">
+        <v>4000</v>
+      </c>
+      <c r="G10" s="11">
+        <v>1600</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="A11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46091</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="11">
+        <v>1350</v>
+      </c>
+      <c r="F11" s="11">
+        <v>4000</v>
+      </c>
+      <c r="G11" s="11">
+        <v>1600</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/industry/CFM/RDIMM.xlsx
+++ b/data/industry/CFM/RDIMM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B70725F-CDB5-479B-A6CD-938802CABCF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9BD0BF-66F3-4BAB-AF7B-F7FDE1B1BD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="610" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="8">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -67,22 +67,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -95,7 +95,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -126,42 +126,42 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -444,18 +444,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45846</v>
       </c>
@@ -501,7 +501,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45860</v>
       </c>
@@ -524,7 +524,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -547,7 +547,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45909</v>
       </c>
@@ -570,7 +570,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45944</v>
       </c>
@@ -593,7 +593,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45972</v>
       </c>
@@ -616,7 +616,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>46000</v>
       </c>
@@ -639,7 +639,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>46028</v>
       </c>
@@ -662,7 +662,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>46063</v>
       </c>
@@ -685,7 +685,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>46091</v>
       </c>
@@ -708,7 +708,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>46119</v>
       </c>
@@ -731,103 +731,135 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="11">
+        <v>250</v>
+      </c>
+      <c r="F13" s="11">
+        <v>400</v>
+      </c>
+      <c r="G13" s="11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="11">
+        <v>250</v>
+      </c>
+      <c r="F14" s="11">
+        <v>500</v>
+      </c>
+      <c r="G14" s="11">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
@@ -841,18 +873,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DCC6B8-7E19-4188-98AA-76DE911B494C}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45846</v>
       </c>
@@ -898,7 +930,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45860</v>
       </c>
@@ -921,7 +953,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -944,7 +976,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45909</v>
       </c>
@@ -967,7 +999,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45944</v>
       </c>
@@ -990,7 +1022,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45972</v>
       </c>
@@ -1013,7 +1045,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>46000</v>
       </c>
@@ -1036,7 +1068,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>46028</v>
       </c>
@@ -1059,7 +1091,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>46063</v>
       </c>
@@ -1082,7 +1114,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>46091</v>
       </c>
@@ -1105,7 +1137,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>46119</v>
       </c>
@@ -1128,103 +1160,135 @@
         <v>450</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="11">
+        <v>300</v>
+      </c>
+      <c r="F13" s="11">
+        <v>800</v>
+      </c>
+      <c r="G13" s="11">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="11">
+        <v>300</v>
+      </c>
+      <c r="F14" s="11">
+        <v>800</v>
+      </c>
+      <c r="G14" s="11">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
@@ -1238,19 +1302,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05E61F2-2635-4C27-8DCB-93976B9195D8}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="12"/>
-    <col min="6" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,7 +1337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45846</v>
       </c>
@@ -1296,7 +1360,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45860</v>
       </c>
@@ -1319,7 +1383,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -1342,7 +1406,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45909</v>
       </c>
@@ -1365,7 +1429,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45944</v>
       </c>
@@ -1388,7 +1452,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45972</v>
       </c>
@@ -1411,7 +1475,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>46000</v>
       </c>
@@ -1434,7 +1498,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>46028</v>
       </c>
@@ -1457,7 +1521,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>46063</v>
       </c>
@@ -1480,7 +1544,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>46091</v>
       </c>
@@ -1503,7 +1567,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>46119</v>
       </c>
@@ -1526,103 +1590,135 @@
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="11">
+        <v>650</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1300</v>
+      </c>
+      <c r="G13" s="11">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="11">
+        <v>650</v>
+      </c>
+      <c r="F14" s="11">
+        <v>1300</v>
+      </c>
+      <c r="G14" s="11">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
@@ -1636,18 +1732,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBC2934-9EA8-4CA1-881F-5F7DC593D698}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1670,7 +1766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45846</v>
       </c>
@@ -1693,7 +1789,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45860</v>
       </c>
@@ -1716,7 +1812,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -1739,7 +1835,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45909</v>
       </c>
@@ -1762,7 +1858,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45944</v>
       </c>
@@ -1785,7 +1881,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45972</v>
       </c>
@@ -1808,7 +1904,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>46000</v>
       </c>
@@ -1831,7 +1927,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>46028</v>
       </c>
@@ -1854,7 +1950,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>46063</v>
       </c>
@@ -1877,7 +1973,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>46091</v>
       </c>
@@ -1900,7 +1996,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>46119</v>
       </c>
@@ -1923,103 +2019,135 @@
         <v>650</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="11">
+        <v>650</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1200</v>
+      </c>
+      <c r="G13" s="11">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="11">
+        <v>715</v>
+      </c>
+      <c r="F14" s="11">
+        <v>1500</v>
+      </c>
+      <c r="G14" s="11">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
@@ -2033,19 +2161,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FF9896-5884-4059-8248-612FA72E9D05}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="12"/>
-    <col min="6" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2068,7 +2196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45846</v>
       </c>
@@ -2091,7 +2219,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45860</v>
       </c>
@@ -2114,7 +2242,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -2137,7 +2265,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45909</v>
       </c>
@@ -2160,7 +2288,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45944</v>
       </c>
@@ -2183,7 +2311,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45972</v>
       </c>
@@ -2206,7 +2334,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>46000</v>
       </c>
@@ -2229,7 +2357,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>46028</v>
       </c>
@@ -2252,7 +2380,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>46063</v>
       </c>
@@ -2275,7 +2403,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>46091</v>
       </c>
@@ -2298,7 +2426,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>46119</v>
       </c>
@@ -2321,103 +2449,135 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="11">
+        <v>1200</v>
+      </c>
+      <c r="F13" s="11">
+        <v>2200</v>
+      </c>
+      <c r="G13" s="11">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="11">
+        <v>1300</v>
+      </c>
+      <c r="F14" s="11">
+        <v>2700</v>
+      </c>
+      <c r="G14" s="11">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
@@ -2431,18 +2591,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1879A24C-F295-4F90-921D-1BCFB04E666C}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2465,7 +2625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45846</v>
       </c>
@@ -2488,7 +2648,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45860</v>
       </c>
@@ -2511,7 +2671,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -2534,7 +2694,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45909</v>
       </c>
@@ -2557,7 +2717,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45944</v>
       </c>
@@ -2580,7 +2740,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45972</v>
       </c>
@@ -2603,7 +2763,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>46000</v>
       </c>
@@ -2626,7 +2786,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>46028</v>
       </c>
@@ -2649,7 +2809,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>46063</v>
       </c>
@@ -2672,7 +2832,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>46091</v>
       </c>
@@ -2695,7 +2855,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>46119</v>
       </c>
@@ -2718,103 +2878,135 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46148</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="11">
+        <v>1950</v>
+      </c>
+      <c r="F13" s="11">
+        <v>3800</v>
+      </c>
+      <c r="G13" s="11">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="11">
+        <v>2100</v>
+      </c>
+      <c r="F14" s="11">
+        <v>3800</v>
+      </c>
+      <c r="G14" s="11">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
